--- a/data/trans_camb/P45C_R1-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R1-Provincia-trans_camb.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,48</t>
+          <t>1,5; 5,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,28</t>
+          <t>1,57; 6,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,19</t>
+          <t>0,35; 3,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,02</t>
+          <t>1,14; 5,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,86</t>
+          <t>1,17; 3,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,72</t>
+          <t>1,76; 4,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,85; -0,23</t>
+          <t>-3,93; -0,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -0,98</t>
+          <t>-4,36; -0,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,94</t>
+          <t>-1,22; 3,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -1,33</t>
+          <t>-4,22; -1,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; -0,06</t>
+          <t>-3,54; -0,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,55</t>
+          <t>-0,06; 4,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; -1,05</t>
+          <t>-3,67; -1,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; -0,88</t>
+          <t>-3,38; -0,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,55</t>
+          <t>0,09; 3,76</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-87,2; 5,45</t>
+          <t>-87,41; 10,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-95,68; -35,29</t>
+          <t>-95,73; -29,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,79; 187,88</t>
+          <t>-34,11; 233,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -51,41</t>
+          <t>-100,0; -33,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,31; 8,91</t>
+          <t>-86,35; 6,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 255,91</t>
+          <t>-4,69; 218,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-90,89; -46,33</t>
+          <t>-92,23; -49,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,98; -38,26</t>
+          <t>-87,19; -36,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 163,82</t>
+          <t>0,5; 175,37</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1124,32 +1124,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,14</t>
+          <t>1,15; 5,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,0</t>
+          <t>-1,5; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,3</t>
+          <t>-0,78; 1,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,95</t>
+          <t>0,72; 2,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,27</t>
+          <t>-0,61; 0,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,57</t>
+          <t>-0,31; 0,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,26</t>
+          <t>-1,34; 4,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 0,27</t>
+          <t>-4,26; 0,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 0,28</t>
+          <t>-4,07; 0,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,97</t>
+          <t>1,88; 5,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,49</t>
+          <t>0,57; 4,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,27</t>
+          <t>-1,33; 0,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,33</t>
+          <t>0,88; 4,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,6</t>
+          <t>-1,3; 1,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; -0,0</t>
+          <t>-2,38; -0,03</t>
         </is>
       </c>
     </row>
@@ -1431,27 +1431,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 254,91</t>
+          <t>-38,61; 281,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-92,69; 48,02</t>
+          <t>-91,99; 27,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-89,42; 62,85</t>
+          <t>-90,01; 42,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56,54; —</t>
+          <t>115,27; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,78; —</t>
+          <t>-23,97; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,04; 427,15</t>
+          <t>24,21; 443,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,17; 175,32</t>
+          <t>-57,06; 146,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-87,54; 14,67</t>
+          <t>-90,37; 13,82</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,0</t>
+          <t>-2,51; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,0</t>
+          <t>-2,16; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,36</t>
+          <t>-0,39; 1,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,0</t>
+          <t>-1,2; 0,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,0</t>
+          <t>-1,18; 0,0</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,59</t>
+          <t>-0,77; 2,6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,56</t>
+          <t>-1,41; 1,52</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,73</t>
+          <t>-0,16; 3,82</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,26</t>
+          <t>-0,67; 3,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,39</t>
+          <t>-0,36; 3,35</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,1</t>
+          <t>0,02; 3,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,21</t>
+          <t>-0,32; 2,27</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,79</t>
+          <t>-0,51; 1,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,21</t>
+          <t>0,47; 3,19</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-55,57; —</t>
+          <t>-58,6; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-33,06; —</t>
+          <t>-36,96; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-48,04; 923,86</t>
+          <t>-50,41; 1009,74</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 824,29</t>
+          <t>-60,98; 650,16</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>20,94; 1374,82</t>
+          <t>-7,98; 1253,48</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,29; -0,14</t>
+          <t>-3,19; -0,08</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,34</t>
+          <t>-3,0; 0,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,03</t>
+          <t>-1,92; 2,13</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,28</t>
+          <t>-3,0; 0,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,82; -0,76</t>
+          <t>-3,99; -0,75</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,2</t>
+          <t>-3,56; 0,19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,59; -0,28</t>
+          <t>-2,46; -0,17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,8; -0,63</t>
+          <t>-2,85; -0,61</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,5</t>
+          <t>-2,11; 0,65</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-89,22; -0,73</t>
+          <t>-87,31; 3,35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-84,75; 37,96</t>
+          <t>-84,96; 77,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-66,52; 116,47</t>
+          <t>-61,03; 141,6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-74,63; 24,47</t>
+          <t>-75,07; 38,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-93,65; -19,89</t>
+          <t>-94,4; -25,97</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-80,51; 15,5</t>
+          <t>-83,33; 11,06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-74,13; -7,74</t>
+          <t>-72,54; -6,99</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-83,81; -22,28</t>
+          <t>-83,38; -23,46</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 27,47</t>
+          <t>-62,97; 37,24</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,73; -0,56</t>
+          <t>-2,73; -0,53</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,49; -0,3</t>
+          <t>-2,42; -0,29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,64</t>
+          <t>-2,09; 0,65</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,51</t>
+          <t>-3,23; -0,64</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,54</t>
+          <t>-3,16; -0,55</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,58; -0,9</t>
+          <t>-3,35; -0,91</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,46; -0,8</t>
+          <t>-2,6; -0,87</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,39; -0,57</t>
+          <t>-2,44; -0,71</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,24; -0,49</t>
+          <t>-2,18; -0,44</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -23,21</t>
+          <t>-100,0; -25,71</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-93,34; -0,48</t>
+          <t>-93,39; -2,24</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-83,35; 62,29</t>
+          <t>-80,25; 73,49</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-91,54; -23,09</t>
+          <t>-89,77; -26,05</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-90,0; -23,0</t>
+          <t>-90,13; -22,45</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-96,0; -43,37</t>
+          <t>-94,88; -40,77</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-90,09; -48,16</t>
+          <t>-89,0; -45,14</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-86,79; -36,13</t>
+          <t>-86,69; -39,33</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-82,29; -26,56</t>
+          <t>-81,41; -24,83</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,16</t>
+          <t>-1,06; 0,15</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,37; -0,21</t>
+          <t>-1,38; -0,22</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,55</t>
+          <t>-0,81; 0,66</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,55</t>
+          <t>-0,72; 0,55</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,04</t>
+          <t>-1,12; 0,01</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,31</t>
+          <t>-0,9; 0,34</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,19</t>
+          <t>-0,7; 0,23</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,07; -0,28</t>
+          <t>-1,1; -0,28</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,32</t>
+          <t>-0,65; 0,28</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 13,58</t>
+          <t>-50,24; 13,51</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-66,82; -12,07</t>
+          <t>-66,36; -11,82</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-40,09; 41,18</t>
+          <t>-41,27; 49,01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 38,2</t>
+          <t>-35,26; 39,83</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-54,64; 3,5</t>
+          <t>-55,31; 4,55</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 24,5</t>
+          <t>-44,33; 25,12</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-34,99; 13,59</t>
+          <t>-35,53; 15,77</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-55,98; -18,82</t>
+          <t>-55,61; -17,9</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 21,06</t>
+          <t>-34,67; 19,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P45C_R1-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R1-Provincia-trans_camb.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,71</t>
+          <t>1,7; 5,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,04</t>
+          <t>1,63; 6,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,8</t>
+          <t>0,34; 4,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,33</t>
+          <t>1,04; 4,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,83</t>
+          <t>1,29; 4,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,64</t>
+          <t>1,65; 4,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>1,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; -0,08</t>
+          <t>-3,85; -0,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -0,86</t>
+          <t>-4,37; -0,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,95</t>
+          <t>-1,17; 4,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -1,32</t>
+          <t>-4,45; -1,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -0,08</t>
+          <t>-3,62; -0,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,35</t>
+          <t>-0,44; 3,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; -1,14</t>
+          <t>-3,44; -1,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -0,96</t>
+          <t>-3,26; -0,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,76</t>
+          <t>-0,08; 3,46</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>52,7%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-87,41; 10,7</t>
+          <t>-89,54; -1,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-95,73; -29,63</t>
+          <t>-95,65; -16,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 233,48</t>
+          <t>-34,41; 232,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -33,48</t>
+          <t>-100,0; -50,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,35; 6,05</t>
+          <t>-87,59; 5,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 218,39</t>
+          <t>-13,73; 219,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-92,23; -49,0</t>
+          <t>-90,66; -46,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,19; -36,06</t>
+          <t>-87,57; -39,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 175,37</t>
+          <t>-4,87; 149,78</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,18</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1124,32 +1124,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,3</t>
+          <t>1,19; 5,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,0</t>
+          <t>-1,51; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,17</t>
+          <t>-0,72; 1,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,92</t>
+          <t>0,72; 3,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,38</t>
+          <t>-0,49; 0,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,63</t>
+          <t>-0,31; 0,73</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>113,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>120,82%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-1,48</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-0,75</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 4,54</t>
+          <t>-1,34; 4,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 0,13</t>
+          <t>-4,13; 0,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 0,22</t>
+          <t>-4,0; 0,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,99</t>
+          <t>1,82; 6,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,23</t>
+          <t>0,57; 4,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,35</t>
+          <t>-0,9; 0,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,59</t>
+          <t>0,84; 4,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,51</t>
+          <t>-1,28; 1,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -0,03</t>
+          <t>-2,12; 0,28</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-58,86%</t>
+          <t>-52,97%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-46,09%</t>
+          <t>-3,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-62,12%</t>
+          <t>-46,43%</t>
         </is>
       </c>
     </row>
@@ -1431,27 +1431,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,61; 281,01</t>
+          <t>-40,36; 285,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-91,99; 27,18</t>
+          <t>-93,06; 35,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-90,01; 42,01</t>
+          <t>-88,51; 60,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>115,27; —</t>
+          <t>94,63; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,97; —</t>
+          <t>-3,08; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,21; 443,12</t>
+          <t>25,33; 418,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-57,06; 146,64</t>
+          <t>-55,55; 160,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-90,37; 13,82</t>
+          <t>-80,65; 62,78</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,0</t>
+          <t>-2,36; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,0</t>
+          <t>-2,12; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,0</t>
+          <t>-2,54; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,17</t>
+          <t>-0,38; 1,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,0</t>
+          <t>-1,05; 0,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,0</t>
+          <t>-1,06; 0,0</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,88</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,7</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,6</t>
+          <t>-0,71; 2,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,52</t>
+          <t>-1,4; 1,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,82</t>
+          <t>-0,3; 3,66</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,27</t>
+          <t>-0,69; 3,32</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,35</t>
+          <t>-0,65; 3,08</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,02; 3,81</t>
+          <t>0,23; 4,02</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,27</t>
+          <t>-0,23; 2,29</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,75</t>
+          <t>-0,5; 1,86</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,19</t>
+          <t>0,52; 3,04</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>220,07%</t>
+          <t>209,39%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>268,95%</t>
+          <t>276,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>243,91%</t>
+          <t>242,49%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-58,6; —</t>
+          <t>-56,6; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-36,96; —</t>
+          <t>-32,26; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 1009,74</t>
+          <t>-38,37; 938,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-60,98; 650,16</t>
+          <t>-64,2; 659,85</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 1253,48</t>
+          <t>24,93; 1425,83</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,31</t>
+          <t>-0,65</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,44</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,08</t>
+          <t>-3,11; -0,03</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,49</t>
+          <t>-2,99; 0,37</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,13</t>
+          <t>-2,01; 1,73</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,45</t>
+          <t>-2,95; 0,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,99; -0,75</t>
+          <t>-3,63; -0,74</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,19</t>
+          <t>-2,47; 1,1</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,46; -0,17</t>
+          <t>-2,5; -0,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; -0,61</t>
+          <t>-2,85; -0,57</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,65</t>
+          <t>-1,78; 0,78</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-6,77%</t>
+          <t>-9,55%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-46,29%</t>
+          <t>-23,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-30,31%</t>
+          <t>-16,92%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-87,31; 3,35</t>
+          <t>-87,71; 8,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-84,96; 77,91</t>
+          <t>-85,32; 43,64</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 141,6</t>
+          <t>-61,06; 142,95</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-75,07; 38,22</t>
+          <t>-75,95; 27,34</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-94,4; -25,97</t>
+          <t>-93,36; -24,23</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-83,33; 11,06</t>
+          <t>-63,81; 69,84</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-72,54; -6,99</t>
+          <t>-72,67; -7,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-83,38; -23,46</t>
+          <t>-82,31; -16,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-62,97; 37,24</t>
+          <t>-54,9; 43,23</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,0</t>
+          <t>-2,02</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-1,18</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,73; -0,53</t>
+          <t>-2,7; -0,5</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -0,29</t>
+          <t>-2,4; -0,19</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,65</t>
+          <t>-1,73; 0,98</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,64</t>
+          <t>-3,13; -0,48</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,16; -0,55</t>
+          <t>-3,11; -0,49</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,35; -0,91</t>
+          <t>-3,45; -0,97</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,6; -0,87</t>
+          <t>-2,46; -0,8</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,44; -0,71</t>
+          <t>-2,45; -0,67</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,18; -0,44</t>
+          <t>-2,12; -0,34</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-36,03%</t>
+          <t>-16,98%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-80,62%</t>
+          <t>-81,48%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-60,71%</t>
+          <t>-55,8%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -25,71</t>
+          <t>-100,0; -24,82</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-93,39; -2,24</t>
+          <t>-93,57; -9,13</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-80,25; 73,49</t>
+          <t>-69,94; 96,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-89,77; -26,05</t>
+          <t>-89,82; -23,86</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-90,13; -22,45</t>
+          <t>-89,45; -19,91</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-94,88; -40,77</t>
+          <t>-95,91; -46,14</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-89,0; -45,14</t>
+          <t>-89,89; -44,56</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-86,69; -39,33</t>
+          <t>-86,45; -38,46</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-81,41; -24,83</t>
+          <t>-78,87; -18,98</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,06</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,15</t>
+          <t>-1,03; 0,23</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,38; -0,22</t>
+          <t>-1,44; -0,16</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,66</t>
+          <t>-0,65; 0,75</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,55</t>
+          <t>-0,7; 0,54</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,01</t>
+          <t>-1,06; 0,05</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,34</t>
+          <t>-0,66; 0,5</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,23</t>
+          <t>-0,67; 0,22</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,1; -0,28</t>
+          <t>-1,08; -0,28</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,28</t>
+          <t>-0,47; 0,4</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-15,48%</t>
+          <t>-7,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-10,41%</t>
+          <t>-3,45%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-50,24; 13,51</t>
+          <t>-50,63; 19,67</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-66,36; -11,82</t>
+          <t>-68,28; -11,51</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-41,27; 49,01</t>
+          <t>-33,46; 54,08</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-35,26; 39,83</t>
+          <t>-34,88; 40,05</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-55,31; 4,55</t>
+          <t>-54,82; 3,57</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-44,33; 25,12</t>
+          <t>-33,96; 36,95</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 15,77</t>
+          <t>-34,16; 15,21</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-55,61; -17,9</t>
+          <t>-55,67; -18,33</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 19,26</t>
+          <t>-25,13; 28,54</t>
         </is>
       </c>
     </row>
